--- a/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplate_country1.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplate_country1.xlsx
@@ -1448,7 +1448,7 @@
       <formula1>"kg,g"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D$1:D$1048576">
-      <formula1>"0.01  保留两位小数四金五入,0.1  保留一位小数四舍五入,0  向下取整，小数舍弃,0.5  进制,1  向上取整，小数进1,2  保留整数，四舍五入"</formula1>
+      <formula1>"0.01  保留两位小数四金五入,0.1  保留一位小数四舍五入,0  向下取整，小数舍弃,0.5  0.5进制,1  向上取整，小数进1,2  保留整数，四舍五入"</formula1>
     </dataValidation>
     <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576 G$1:G$1048576">
       <formula1>32874</formula1>

--- a/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplate_country1.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplate_country1.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -1459,26 +1457,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplate_country1.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplate_country1.xlsx
@@ -148,26 +148,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>失效日期</t>
-    </r>
+    <t>失效日期</t>
   </si>
   <si>
     <r>
@@ -985,12 +966,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1385,7 +1369,7 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
@@ -1435,7 +1419,7 @@
       </c>
     </row>
     <row r="2" spans="6:6">
-      <c r="F2" s="3"/>
+      <c r="F2" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="4">
@@ -1448,7 +1432,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D$1:D$1048576">
       <formula1>"0.01  保留两位小数四金五入,0.1  保留一位小数四舍五入,0  向下取整，小数舍弃,0.5  0.5进制,1  向上取整，小数进1,2  保留整数，四舍五入"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576 G$1:G$1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576 G2:G1048576">
       <formula1>32874</formula1>
       <formula2>398117</formula2>
     </dataValidation>
